--- a/dynamical_DE_nonfid/cmb/highl_so_fisher.xlsx
+++ b/dynamical_DE_nonfid/cmb/highl_so_fisher.xlsx
@@ -487,34 +487,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>210947997.1039099</v>
+        <v>207513310.0375457</v>
       </c>
       <c r="C2" t="n">
-        <v>-748031965.8610566</v>
+        <v>-733071196.8305918</v>
       </c>
       <c r="D2" t="n">
-        <v>162627817.3660116</v>
+        <v>160235529.0545499</v>
       </c>
       <c r="E2" t="n">
-        <v>-5257008.076118838</v>
+        <v>-5101251.607018161</v>
       </c>
       <c r="F2" t="n">
-        <v>-66888170.26729821</v>
+        <v>-65895543.60427935</v>
       </c>
       <c r="G2" t="n">
-        <v>-14502671.84934269</v>
+        <v>-14305276.14288187</v>
       </c>
       <c r="H2" t="n">
-        <v>-7542359.874541962</v>
+        <v>-7413137.86584538</v>
       </c>
       <c r="I2" t="n">
-        <v>52011192.43369181</v>
+        <v>51253245.30159964</v>
       </c>
       <c r="J2" t="n">
-        <v>2244324.138680811</v>
+        <v>2141418.797902582</v>
       </c>
       <c r="K2" t="n">
-        <v>273237.2372825897</v>
+        <v>251735.0090826074</v>
       </c>
     </row>
     <row r="3">
@@ -524,34 +524,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-748031965.8610566</v>
+        <v>-733071196.8305918</v>
       </c>
       <c r="C3" t="n">
-        <v>3040602831.425878</v>
+        <v>2968142634.464968</v>
       </c>
       <c r="D3" t="n">
-        <v>-529314235.9539289</v>
+        <v>-520203223.7791474</v>
       </c>
       <c r="E3" t="n">
-        <v>32775933.15315635</v>
+        <v>31939420.66808374</v>
       </c>
       <c r="F3" t="n">
-        <v>242545574.7319359</v>
+        <v>237816516.00161</v>
       </c>
       <c r="G3" t="n">
-        <v>51636789.67750655</v>
+        <v>50658246.07685389</v>
       </c>
       <c r="H3" t="n">
-        <v>25518755.00227864</v>
+        <v>25012718.86772778</v>
       </c>
       <c r="I3" t="n">
-        <v>-187022014.9918945</v>
+        <v>-183412050.0531373</v>
       </c>
       <c r="J3" t="n">
-        <v>-9183716.114923943</v>
+        <v>-8904933.64392023</v>
       </c>
       <c r="K3" t="n">
-        <v>-1258787.493324667</v>
+        <v>-1209113.105635059</v>
       </c>
     </row>
     <row r="4">
@@ -561,34 +561,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>162627817.3660116</v>
+        <v>160235529.0545499</v>
       </c>
       <c r="C4" t="n">
-        <v>-529314235.9539291</v>
+        <v>-520203223.7791474</v>
       </c>
       <c r="D4" t="n">
-        <v>135417788.0830569</v>
+        <v>133464729.8643146</v>
       </c>
       <c r="E4" t="n">
-        <v>-2483051.662714934</v>
+        <v>-2406243.967573083</v>
       </c>
       <c r="F4" t="n">
-        <v>-46560180.16081008</v>
+        <v>-45996629.70974699</v>
       </c>
       <c r="G4" t="n">
-        <v>-9697699.677639376</v>
+        <v>-9599886.153403858</v>
       </c>
       <c r="H4" t="n">
-        <v>-6430456.886140045</v>
+        <v>-6324074.610816896</v>
       </c>
       <c r="I4" t="n">
-        <v>36260575.37079487</v>
+        <v>35832945.04691161</v>
       </c>
       <c r="J4" t="n">
-        <v>3850580.42627414</v>
+        <v>3720253.704766751</v>
       </c>
       <c r="K4" t="n">
-        <v>760569.3628585916</v>
+        <v>730411.440091668</v>
       </c>
     </row>
     <row r="5">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5257008.076118838</v>
+        <v>-5101251.607018161</v>
       </c>
       <c r="C5" t="n">
-        <v>32775933.15315635</v>
+        <v>31939420.66808375</v>
       </c>
       <c r="D5" t="n">
-        <v>-2483051.662714934</v>
+        <v>-2406243.967573083</v>
       </c>
       <c r="E5" t="n">
-        <v>1067773.522959887</v>
+        <v>1053937.55755262</v>
       </c>
       <c r="F5" t="n">
-        <v>1895938.290935782</v>
+        <v>1838346.652671678</v>
       </c>
       <c r="G5" t="n">
-        <v>364246.9644654525</v>
+        <v>351384.3876943235</v>
       </c>
       <c r="H5" t="n">
-        <v>127534.2582620264</v>
+        <v>123591.4912733995</v>
       </c>
       <c r="I5" t="n">
-        <v>-1429359.328450104</v>
+        <v>-1384353.652142614</v>
       </c>
       <c r="J5" t="n">
-        <v>-134133.9779909615</v>
+        <v>-135030.6753919362</v>
       </c>
       <c r="K5" t="n">
-        <v>-25477.79673560329</v>
+        <v>-25951.35500270786</v>
       </c>
     </row>
     <row r="6">
@@ -635,34 +635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-66888170.2672982</v>
+        <v>-65895543.60427935</v>
       </c>
       <c r="C6" t="n">
-        <v>242545574.7319359</v>
+        <v>237816516.00161</v>
       </c>
       <c r="D6" t="n">
-        <v>-46560180.16081007</v>
+        <v>-45996629.70974699</v>
       </c>
       <c r="E6" t="n">
-        <v>1895938.290935782</v>
+        <v>1838346.652671678</v>
       </c>
       <c r="F6" t="n">
-        <v>26281289.85686906</v>
+        <v>25902436.09238109</v>
       </c>
       <c r="G6" t="n">
-        <v>6206117.597213352</v>
+        <v>6120874.161781616</v>
       </c>
       <c r="H6" t="n">
-        <v>1857490.771640951</v>
+        <v>1830551.311384381</v>
       </c>
       <c r="I6" t="n">
-        <v>-20415867.0216278</v>
+        <v>-20127851.15690659</v>
       </c>
       <c r="J6" t="n">
-        <v>1729073.081258414</v>
+        <v>1716667.314444764</v>
       </c>
       <c r="K6" t="n">
-        <v>543296.7232725524</v>
+        <v>538627.9344067173</v>
       </c>
     </row>
     <row r="7">
@@ -672,34 +672,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-14502671.84934269</v>
+        <v>-14305276.14288187</v>
       </c>
       <c r="C7" t="n">
-        <v>51636789.67750655</v>
+        <v>50658246.07685387</v>
       </c>
       <c r="D7" t="n">
-        <v>-9697699.677639376</v>
+        <v>-9599886.153403858</v>
       </c>
       <c r="E7" t="n">
-        <v>364246.9644654525</v>
+        <v>351384.3876943235</v>
       </c>
       <c r="F7" t="n">
-        <v>6206117.597213352</v>
+        <v>6120874.161781616</v>
       </c>
       <c r="G7" t="n">
-        <v>1520622.261850424</v>
+        <v>1500434.014689434</v>
       </c>
       <c r="H7" t="n">
-        <v>349516.3185401252</v>
+        <v>345343.8599135474</v>
       </c>
       <c r="I7" t="n">
-        <v>-4847271.042006001</v>
+        <v>-4781944.094391508</v>
       </c>
       <c r="J7" t="n">
-        <v>650763.1142649917</v>
+        <v>643391.5897685046</v>
       </c>
       <c r="K7" t="n">
-        <v>188894.4962308991</v>
+        <v>186698.7128325448</v>
       </c>
     </row>
     <row r="8">
@@ -709,34 +709,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-7542359.874541963</v>
+        <v>-7413137.86584538</v>
       </c>
       <c r="C8" t="n">
-        <v>25518755.00227864</v>
+        <v>25012718.86772778</v>
       </c>
       <c r="D8" t="n">
-        <v>-6430456.886140045</v>
+        <v>-6324074.610816896</v>
       </c>
       <c r="E8" t="n">
-        <v>127534.2582620264</v>
+        <v>123591.4912733994</v>
       </c>
       <c r="F8" t="n">
-        <v>1857490.771640951</v>
+        <v>1830551.311384381</v>
       </c>
       <c r="G8" t="n">
-        <v>349516.3185401252</v>
+        <v>345343.8599135474</v>
       </c>
       <c r="H8" t="n">
-        <v>328989.7128407154</v>
+        <v>322878.7924313071</v>
       </c>
       <c r="I8" t="n">
-        <v>-1441830.971849905</v>
+        <v>-1421410.760232322</v>
       </c>
       <c r="J8" t="n">
-        <v>-335049.5097072185</v>
+        <v>-326319.0542621494</v>
       </c>
       <c r="K8" t="n">
-        <v>-75594.17434015693</v>
+        <v>-73529.15618616104</v>
       </c>
     </row>
     <row r="9">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52011192.43369181</v>
+        <v>51253245.30159964</v>
       </c>
       <c r="C9" t="n">
-        <v>-187022014.9918945</v>
+        <v>-183412050.0531372</v>
       </c>
       <c r="D9" t="n">
-        <v>36260575.37079487</v>
+        <v>35832945.04691161</v>
       </c>
       <c r="E9" t="n">
-        <v>-1429359.328450104</v>
+        <v>-1384353.652142614</v>
       </c>
       <c r="F9" t="n">
-        <v>-20415867.0216278</v>
+        <v>-20127851.15690659</v>
       </c>
       <c r="G9" t="n">
-        <v>-4847271.042006001</v>
+        <v>-4781944.094391508</v>
       </c>
       <c r="H9" t="n">
-        <v>-1441830.971849904</v>
+        <v>-1421410.760232322</v>
       </c>
       <c r="I9" t="n">
-        <v>15940605.57622786</v>
+        <v>15719434.87317739</v>
       </c>
       <c r="J9" t="n">
-        <v>-1388313.965896982</v>
+        <v>-1378350.810876114</v>
       </c>
       <c r="K9" t="n">
-        <v>-433834.8137381457</v>
+        <v>-430137.6318188451</v>
       </c>
     </row>
     <row r="10">
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2244324.138680811</v>
+        <v>2141418.797902581</v>
       </c>
       <c r="C10" t="n">
-        <v>-9183716.114923943</v>
+        <v>-8904933.643920232</v>
       </c>
       <c r="D10" t="n">
-        <v>3850580.426274141</v>
+        <v>3720253.704766751</v>
       </c>
       <c r="E10" t="n">
-        <v>-134133.9779909615</v>
+        <v>-135030.6753919362</v>
       </c>
       <c r="F10" t="n">
-        <v>1729073.081258414</v>
+        <v>1716667.314444764</v>
       </c>
       <c r="G10" t="n">
-        <v>650763.1142649917</v>
+        <v>643391.5897685046</v>
       </c>
       <c r="H10" t="n">
-        <v>-335049.5097072185</v>
+        <v>-326319.0542621494</v>
       </c>
       <c r="I10" t="n">
-        <v>-1388313.965896982</v>
+        <v>-1378350.810876114</v>
       </c>
       <c r="J10" t="n">
-        <v>1272142.561197626</v>
+        <v>1249055.900837815</v>
       </c>
       <c r="K10" t="n">
-        <v>324755.9587317336</v>
+        <v>318945.5342699972</v>
       </c>
     </row>
     <row r="11">
@@ -820,34 +820,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273237.2372825898</v>
+        <v>251735.0090826073</v>
       </c>
       <c r="C11" t="n">
-        <v>-1258787.493324667</v>
+        <v>-1209113.105635059</v>
       </c>
       <c r="D11" t="n">
-        <v>760569.3628585916</v>
+        <v>730411.4400916682</v>
       </c>
       <c r="E11" t="n">
-        <v>-25477.79673560329</v>
+        <v>-25951.35500270785</v>
       </c>
       <c r="F11" t="n">
-        <v>543296.7232725524</v>
+        <v>538627.9344067173</v>
       </c>
       <c r="G11" t="n">
-        <v>188894.4962308991</v>
+        <v>186698.7128325448</v>
       </c>
       <c r="H11" t="n">
-        <v>-75594.17434015693</v>
+        <v>-73529.15618616104</v>
       </c>
       <c r="I11" t="n">
-        <v>-433834.8137381457</v>
+        <v>-430137.6318188452</v>
       </c>
       <c r="J11" t="n">
-        <v>324755.9587317336</v>
+        <v>318945.534269997</v>
       </c>
       <c r="K11" t="n">
-        <v>83342.03204443978</v>
+        <v>81873.13907865835</v>
       </c>
     </row>
   </sheetData>
